--- a/reports/weekly_operation_20260615.xlsx
+++ b/reports/weekly_operation_20260615.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -574,17 +574,17 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/reports/weekly_operation_20260615.xlsx
+++ b/reports/weekly_operation_20260615.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -574,17 +574,17 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -595,15 +595,36 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>微信</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -658,13 +679,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -674,13 +695,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
